--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1628,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI8"/>
+  <dimension ref="A1:BI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46111.79166666666</v>
+        <v>46111.75</v>
       </c>
     </row>
     <row r="8">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,6 +2118,203 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
+        <v>46111.79166666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" s="3" t="n">
         <v>46111.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46111.5625</v>
+        <v>46111.5</v>
       </c>
     </row>
     <row r="4">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46111.64583333334</v>
+        <v>46111.5625</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46111.64583333334</v>
+        <v>46111.57291666666</v>
       </c>
     </row>
     <row r="6">
@@ -1536,27 +1536,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1628,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46111.66666666666</v>
+        <v>46111.64583333334</v>
       </c>
     </row>
     <row r="7">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46111.75</v>
+        <v>46111.64583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46111.79166666666</v>
+        <v>46111.66666666666</v>
       </c>
     </row>
     <row r="9">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -2315,6 +2315,597 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
+        <v>46111.66666666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>46111.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Racing United</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" s="3" t="n">
+        <v>46111.79166666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" s="3" t="n">
         <v>46111.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1204,70 +1204,70 @@
         <v>5.05</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2022,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R7" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R6" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2189,34 +2189,34 @@
         <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
         <v>1.83</v>
@@ -2225,88 +2225,88 @@
         <v>1.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R7" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R6" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>5.48</v>
+        <v>4.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>4.51</v>
+        <v>5.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1273,40 +1273,40 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="BB4" t="n">
         <v>1.28</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S6" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="U6" t="n">
-        <v>4.51</v>
+        <v>5.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R7" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>5.48</v>
+        <v>4.51</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="X7" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R6" t="n">
-        <v>5.35</v>
+        <v>3.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.38</v>
+        <v>2.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>5.48</v>
+        <v>4.51</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>2.53</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.17</v>
+        <v>1.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>3.33</v>
+        <v>5.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>4.51</v>
+        <v>5.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.44</v>
+        <v>2.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.75</v>
+        <v>3.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1195,19 +1195,19 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>5.05</v>
+        <v>3.85</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
         <v>5.25</v>
@@ -1219,7 +1219,7 @@
         <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="Y4" t="n">
         <v>1.28</v>
@@ -1243,7 +1243,7 @@
         <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG4" t="n">
         <v>4.1</v>
@@ -1252,16 +1252,16 @@
         <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AM4" t="n">
         <v>1.3</v>
@@ -1303,7 +1303,7 @@
         <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="BA4" t="n">
         <v>4.53</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
       </c>
       <c r="R3" t="n">
         <v>2.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>3.85</v>
+        <v>4.68</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
@@ -1240,13 +1240,13 @@
         <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
         <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="AH4" t="n">
         <v>1.16</v>
@@ -1273,40 +1273,40 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="BB4" t="n">
         <v>1.28</v>
@@ -1401,70 +1401,70 @@
         <v>6.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="R6" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="S6" t="n">
-        <v>2.93</v>
+        <v>2.51</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.51</v>
+        <v>4.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.47</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.75</v>
+        <v>2.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>5.35</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
-        <v>2.38</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>5.48</v>
+        <v>4.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="W7" t="n">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.22</v>
+        <v>2.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS8" t="n">
         <v>3.25</v>
       </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.86</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>3.8</v>
+        <v>6.39</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.3</v>
+        <v>2.59</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.38</v>
+        <v>2.91</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
         <v>3.12</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1201,7 +1201,7 @@
         <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>4.68</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
@@ -2028,7 +2028,7 @@
         <v>1.96</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AF8" t="n">
         <v>1.3</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="R10" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.09</v>
-      </c>
       <c r="U6" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W6" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="X6" t="n">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.31</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AN6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BD6" t="n">
         <v>2.92</v>
       </c>
-      <c r="AE6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.42</v>
-      </c>
       <c r="BE6" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>2.51</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="U7" t="n">
-        <v>4.46</v>
+        <v>4.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>2.97</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.53</v>
+        <v>2.24</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1395,19 +1395,19 @@
         <v>1.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
         <v>2.04</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="U5" t="n">
-        <v>7.17</v>
+        <v>7.28</v>
       </c>
       <c r="V5" t="n">
         <v>1.42</v>
@@ -1416,10 +1416,10 @@
         <v>2.56</v>
       </c>
       <c r="X5" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
         <v>6.8</v>
@@ -1440,10 +1440,10 @@
         <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="AH5" t="n">
         <v>1.21</v>
@@ -1455,10 +1455,10 @@
         <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AM5" t="n">
         <v>1.18</v>
@@ -1592,25 +1592,25 @@
         <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
         <v>4.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
         <v>3.42</v>
@@ -1631,25 +1631,25 @@
         <v>1.49</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG6" t="n">
         <v>3.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" t="n">
         <v>9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK6" t="n">
         <v>2.03</v>
@@ -1658,10 +1658,10 @@
         <v>1.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
         <v>3.75</v>
       </c>
       <c r="S7" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
         <v>4.25</v>
@@ -1807,10 +1807,10 @@
         <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="X7" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="Y7" t="n">
         <v>1.3</v>
@@ -1831,10 +1831,10 @@
         <v>2.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
         <v>2.95</v>
@@ -1843,7 +1843,7 @@
         <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.03</v>
@@ -1852,7 +1852,7 @@
         <v>1.85</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AM7" t="n">
         <v>1.21</v>
@@ -1903,13 +1903,13 @@
         <v>1.23</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BD7" t="n">
         <v>3.42</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="BF7" t="n">
         <v>1.1</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="S9" t="n">
         <v>2.38</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
         <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="S4" t="n">
         <v>2.39</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>3.7</v>
+        <v>4.31</v>
       </c>
       <c r="S8" t="n">
         <v>2.99</v>
@@ -2028,10 +2028,10 @@
         <v>1.96</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AG8" t="n">
         <v>6.8</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
         <v>4.04</v>
@@ -1076,40 +1076,40 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB3" t="n">
         <v>1.28</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="S5" t="n">
         <v>2.04</v>
@@ -1437,10 +1437,10 @@
         <v>2.92</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
         <v>3.65</v>
@@ -1470,40 +1470,40 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="BB5" t="n">
         <v>1.25</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.2</v>
       </c>
       <c r="S6" t="n">
         <v>2.98</v>
@@ -1667,40 +1667,40 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="BB6" t="n">
         <v>1.32</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="S7" t="n">
         <v>2.47</v>
@@ -1831,10 +1831,10 @@
         <v>2.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
         <v>2.95</v>
@@ -1864,40 +1864,40 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="BB7" t="n">
         <v>1.23</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
-        <v>4.31</v>
+        <v>5.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="U8" t="n">
-        <v>5.93</v>
+        <v>6.39</v>
       </c>
       <c r="V8" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK8" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.18</v>
+        <v>2.59</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.41</v>
+        <v>2.91</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R9" t="n">
-        <v>4.6</v>
+        <v>4.31</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="U9" t="n">
-        <v>6.39</v>
+        <v>5.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>1.92</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>3.51</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
         <v>2.3</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.59</v>
+        <v>3.18</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.91</v>
+        <v>2.41</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
         <v>3.54</v>
@@ -810,70 +810,70 @@
         <v>2.68</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="R4" t="n">
         <v>4.36</v>
@@ -1219,7 +1219,7 @@
         <v>2.5</v>
       </c>
       <c r="X4" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
         <v>1.28</v>
@@ -1234,7 +1234,7 @@
         <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
         <v>2.74</v>
@@ -1246,13 +1246,13 @@
         <v>1.64</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="AH4" t="n">
         <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.01</v>
@@ -1276,37 +1276,37 @@
         <v>1.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.34</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.52</v>
+        <v>4.53</v>
       </c>
       <c r="BB4" t="n">
         <v>1.28</v>
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
         <v>1.82</v>
@@ -1610,10 +1610,10 @@
         <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Y6" t="n">
         <v>1.23</v>
@@ -1628,10 +1628,10 @@
         <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AE6" t="n">
         <v>2.5</v>
@@ -1640,19 +1640,19 @@
         <v>1.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AH6" t="n">
         <v>1.13</v>
       </c>
       <c r="AI6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL6" t="n">
         <v>1.67</v>
@@ -1673,7 +1673,7 @@
         <v>2.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.46</v>
+        <v>2.66</v>
       </c>
       <c r="AS6" t="n">
         <v>3.83</v>
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="R7" t="n">
-        <v>4.13</v>
+        <v>4.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>4.25</v>
+        <v>5.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
@@ -1825,40 +1825,40 @@
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="AE7" t="n">
         <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
         <v>2.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1894,25 +1894,25 @@
         <v>1.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="BA7" t="n">
         <v>4.74</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2189,103 +2189,103 @@
         <v>4.31</v>
       </c>
       <c r="S9" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="T9" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="U9" t="n">
-        <v>5.93</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
         <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AI9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1.53</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AR9" t="n">
-        <v>2.48</v>
+        <v>1.89</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.25</v>
+        <v>2.41</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.3</v>
+        <v>3.21</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ9" t="n">
         <v>1.53</v>
@@ -2294,19 +2294,19 @@
         <v>2.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="R10" t="n">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="S2" t="n">
         <v>2.47</v>
@@ -852,22 +852,22 @@
         <v>2.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AH2" t="n">
         <v>1.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AM2" t="n">
         <v>1.15</v>
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
         <v>4.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
@@ -1237,19 +1237,19 @@
         <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AE4" t="n">
         <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
         <v>4.05</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI4" t="n">
         <v>8.5</v>
@@ -1258,16 +1258,16 @@
         <v>1.01</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>1.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AS4" t="n">
         <v>2.61</v>
@@ -1294,7 +1294,7 @@
         <v>2.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AX4" t="n">
         <v>1.41</v>
@@ -1309,16 +1309,16 @@
         <v>4.53</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BF4" t="n">
         <v>1.08</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
-        <v>4.46</v>
+        <v>5.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.9</v>
+        <v>4.61</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>5.54</v>
+        <v>4.46</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="X7" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.32</v>
       </c>
-      <c r="AD7" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AW7" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>4.31</v>
@@ -2258,40 +2258,40 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.21</v>
+        <v>2.86</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="BB9" t="n">
         <v>1.53</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2580,73 +2580,73 @@
         <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.62</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="R6" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>1.82</v>
       </c>
       <c r="U6" t="n">
-        <v>5.54</v>
+        <v>4.46</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="W6" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="X6" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.32</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF6" t="n">
+      <c r="AN6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG6" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AW6" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="U7" t="n">
-        <v>4.46</v>
+        <v>5.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>7.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.9</v>
+        <v>4.61</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.24</v>
+        <v>4.74</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -787,17 +787,17 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -998,61 +998,61 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Q3" t="n">
         <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="S3" t="n">
-        <v>4.04</v>
+        <v>5.09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="V3" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE3" t="n">
         <v>2.41</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.25</v>
+        <v>3.95</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -1061,16 +1061,16 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>1.71</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="R4" t="n">
         <v>4.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="U4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X4" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
@@ -1234,25 +1234,25 @@
         <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.01</v>
@@ -1267,7 +1267,7 @@
         <v>1.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>1.61</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="AS4" t="n">
         <v>2.61</v>
@@ -1294,7 +1294,7 @@
         <v>2.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AX4" t="n">
         <v>1.41</v>
@@ -1312,13 +1312,13 @@
         <v>1.27</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BD4" t="n">
         <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
         <v>1.08</v>
@@ -1401,70 +1401,70 @@
         <v>6.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="T5" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
-        <v>7.28</v>
+        <v>8.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="W5" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="X5" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="AE5" t="n">
         <v>2.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>7.39</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1601,67 +1601,67 @@
         <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1697,25 +1697,25 @@
         <v>1.05</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BA6" t="n">
         <v>3.24</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="U7" t="n">
-        <v>5.54</v>
+        <v>4.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="X7" t="n">
         <v>2.92</v>
@@ -1816,34 +1816,34 @@
         <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
         <v>1.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.04</v>
@@ -1852,67 +1852,67 @@
         <v>1.91</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.14</v>
+        <v>2.56</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.61</v>
+        <v>3.53</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,28 +1983,28 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U8" t="n">
-        <v>6.39</v>
+        <v>6.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X8" t="n">
         <v>3.5</v>
@@ -2019,7 +2019,7 @@
         <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
         <v>1.49</v>
@@ -2028,34 +2028,34 @@
         <v>2.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
         <v>1.44</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AH8" t="n">
         <v>1.12</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>4.31</v>
+        <v>3.95</v>
       </c>
       <c r="S9" t="n">
         <v>3.75</v>
@@ -2216,7 +2216,7 @@
         <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AC9" t="n">
         <v>1.78</v>
@@ -2234,7 +2234,7 @@
         <v>7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AI9" t="n">
         <v>17.5</v>
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2574,37 +2574,37 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="R11" t="n">
-        <v>4.65</v>
+        <v>6.2</v>
       </c>
       <c r="S11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.14</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U11" t="n">
-        <v>5.62</v>
+        <v>6.23</v>
       </c>
       <c r="V11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.36</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AA11" t="n">
         <v>1.07</v>
@@ -2613,40 +2613,40 @@
         <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.65</v>
+        <v>5.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI12"/>
+  <dimension ref="A1:BI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4.4</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>3.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.74</v>
+        <v>4.86</v>
       </c>
       <c r="S3" t="n">
-        <v>5.09</v>
+        <v>2.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>2.76</v>
+        <v>5.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="X3" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.49</v>
+        <v>2.78</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AH3" t="n">
         <v>1.16</v>
       </c>
       <c r="AI3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.17</v>
+        <v>2.05</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="BI3" s="3" t="n">
-        <v>46111.5</v>
+        <v>46111.5625</v>
       </c>
     </row>
     <row r="4">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="R4" t="n">
-        <v>4.36</v>
+        <v>4.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.04</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,52 +1276,52 @@
         <v>1.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>46111.5625</v>
+        <v>46111.64583333334</v>
       </c>
     </row>
     <row r="5">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R5" t="n">
-        <v>6.25</v>
+        <v>3.2</v>
       </c>
       <c r="S5" t="n">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>8.25</v>
+        <v>4.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
         <v>2.31</v>
       </c>
       <c r="X5" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="Y5" t="n">
         <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
         <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.11</v>
+        <v>3.83</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.54</v>
+        <v>5.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.51</v>
+        <v>2.17</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AX5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46111.57291666666</v>
+        <v>46111.64583333334</v>
       </c>
     </row>
     <row r="6">
@@ -1536,27 +1536,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.24</v>
+        <v>3.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.15</v>
+        <v>7</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.01</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="AR6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AS6" t="n">
         <v>2.66</v>
       </c>
-      <c r="AS6" t="n">
-        <v>3.83</v>
-      </c>
       <c r="AT6" t="n">
-        <v>5.9</v>
+        <v>3.72</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AV6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.7</v>
       </c>
-      <c r="AW6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BA6" t="n">
-        <v>3.24</v>
+        <v>2.48</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.12</v>
+        <v>2.38</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>46111.64583333334</v>
+        <v>46111.66666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>4.67</v>
+        <v>2.85</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1921,7 +1921,7 @@
         <v>0</v>
       </c>
       <c r="BI7" s="3" t="n">
-        <v>46111.64583333334</v>
+        <v>46111.75</v>
       </c>
     </row>
     <row r="8">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,80 +1983,80 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>3.78</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="U8" t="n">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="V8" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>2.67</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.1</v>
+        <v>5.85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN8" t="n">
         <v>2.32</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.59</v>
+        <v>2.08</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.91</v>
+        <v>3.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46111.66666666666</v>
+        <v>46111.79166666666</v>
       </c>
     </row>
     <row r="9">
@@ -2127,27 +2127,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="R9" t="n">
-        <v>3.95</v>
+        <v>1.68</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,597 +2315,6 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46111.66666666666</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="3" t="n">
-        <v>46111.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Racing United</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Treasure Beach</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="3" t="n">
-        <v>46111.79166666666</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mount Pleasant Academy FC</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3" t="n">
         <v>46111.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="R4" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
         <v>4.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB4" t="n">
         <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.04</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN4" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.01</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>2.56</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AV4" t="n">
         <v>2.19</v>
@@ -1300,7 +1300,7 @@
         <v>1.42</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AZ4" t="n">
         <v>1.4</v>
@@ -1312,13 +1312,13 @@
         <v>1.21</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
         <v>3.58</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="BF4" t="n">
         <v>1.12</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="R3" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="S3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>5.35</v>
@@ -1022,13 +1022,13 @@
         <v>2.56</v>
       </c>
       <c r="X3" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
@@ -1037,40 +1037,40 @@
         <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG3" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>4.53</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BA4" t="n">
-        <v>4.6</v>
+        <v>3.24</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.85</v>
       </c>
-      <c r="U5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN5" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.03</v>
+        <v>1.59</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.83</v>
+        <v>2.56</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.24</v>
+        <v>4.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="R8" t="n">
-        <v>6.2</v>
+        <v>5.43</v>
       </c>
       <c r="S8" t="n">
         <v>2.07</v>
       </c>
       <c r="T8" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="U8" t="n">
-        <v>6.23</v>
+        <v>5.3</v>
       </c>
       <c r="V8" t="n">
         <v>1.38</v>
@@ -2007,19 +2007,19 @@
         <v>2.67</v>
       </c>
       <c r="X8" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z8" t="n">
         <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
         <v>1.3</v>
@@ -2028,34 +2028,34 @@
         <v>3.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,112 +2180,112 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN9" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,6 +2315,203 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
+        <v>46111.83333333334</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" s="3" t="n">
         <v>46111.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -998,19 +998,19 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R3" t="n">
-        <v>4.8</v>
+        <v>4.86</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
         <v>5.35</v>
@@ -1022,109 +1022,109 @@
         <v>2.56</v>
       </c>
       <c r="X3" t="n">
-        <v>3.16</v>
+        <v>3.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AM3" t="n">
         <v>1.32</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.62</v>
+        <v>3.43</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7</v>
+        <v>4.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="T4" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1</v>
+        <v>5.48</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="X4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG4" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BA4" t="n">
-        <v>3.24</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.14</v>
+        <v>3.76</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>4.43</v>
+        <v>3.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>4.8</v>
+        <v>4.89</v>
       </c>
       <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.4</v>
       </c>
-      <c r="W5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AD5" t="n">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.34</v>
+        <v>3.98</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.75</v>
+        <v>8.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.56</v>
+        <v>3.44</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.5</v>
+        <v>5.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.74</v>
+        <v>1.42</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="R6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="S6" t="n">
         <v>3.75</v>
@@ -1667,40 +1667,40 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.32</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.68</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BA6" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="BB6" t="n">
         <v>1.53</v>
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
         <v>3.2</v>
       </c>
       <c r="R7" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE7" t="n">
         <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1983,55 +1983,55 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.62</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>5.43</v>
+        <v>4.46</v>
       </c>
       <c r="S8" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="U8" t="n">
-        <v>5.3</v>
+        <v>6.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
         <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="AE8" t="n">
         <v>1.86</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>3.2</v>
@@ -2046,16 +2046,16 @@
         <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BC8" t="n">
         <v>2.11</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
         <v>1.63</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="S9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.51</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U9" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.04</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AL9" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4.3</v>
+        <v>3.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE10" t="n">
         <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -969,32 +969,32 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.46</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4.47</v>
+        <v>3.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>5.48</v>
+        <v>4.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="X4" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.11</v>
+        <v>2.69</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1.8</v>
       </c>
-      <c r="AG4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AW4" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U5" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="AF5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG5" t="n">
         <v>3.2</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AH5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BA5" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.14</v>
+        <v>3.76</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1166,32 +1166,32 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1363,32 +1363,32 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1575,17 +1575,17 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1786,22 +1786,22 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="R7" t="n">
-        <v>2.87</v>
+        <v>3.75</v>
       </c>
       <c r="S7" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>4.32</v>
+        <v>3.85</v>
       </c>
       <c r="V7" t="n">
         <v>1.39</v>
@@ -1810,19 +1810,19 @@
         <v>2.66</v>
       </c>
       <c r="X7" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
         <v>1.26</v>
@@ -1831,7 +1831,7 @@
         <v>3.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
         <v>1.8</v>
@@ -1840,7 +1840,7 @@
         <v>3.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AI7" t="n">
         <v>6.4</v>
@@ -1849,16 +1849,16 @@
         <v>1.07</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1891,25 +1891,25 @@
         <v>1.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AZ7" t="n">
         <v>1.54</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.36</v>
+        <v>2.76</v>
       </c>
       <c r="BB7" t="n">
         <v>1.21</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BD7" t="n">
         <v>3.58</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BF7" t="n">
         <v>1.15</v>
@@ -1983,28 +1983,28 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
         <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
       <c r="S8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.22</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.01</v>
-      </c>
       <c r="U8" t="n">
-        <v>6.19</v>
+        <v>7.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="X8" t="n">
         <v>2.83</v>
@@ -2013,10 +2013,10 @@
         <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
         <v>1.03</v>
@@ -2028,88 +2028,88 @@
         <v>3.05</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF8" t="n">
         <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AM8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
         <v>1.23</v>
       </c>
-      <c r="AN8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BC8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2186,28 +2186,28 @@
         <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>7.9</v>
+        <v>4.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="T9" t="n">
         <v>2.7</v>
       </c>
       <c r="U9" t="n">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="X9" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
         <v>4.9</v>
@@ -2222,37 +2222,37 @@
         <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AG9" t="n">
         <v>2.56</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AM9" t="n">
         <v>1.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>1.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BD9" t="n">
         <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="BF9" t="n">
         <v>1.28</v>
@@ -2380,7 +2380,7 @@
         <v>3.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="R10" t="n">
         <v>1.85</v>
@@ -2392,7 +2392,7 @@
         <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="V10" t="n">
         <v>1.44</v>
@@ -2401,7 +2401,7 @@
         <v>2.47</v>
       </c>
       <c r="X10" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
         <v>1.3</v>
@@ -2416,28 +2416,28 @@
         <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AI10" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
         <v>1.88</v>
@@ -2500,7 +2500,7 @@
         <v>3.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="BF10" t="n">
         <v>1.12</v>

--- a/jogos_2026-03-30.xlsx
+++ b/jogos_2026-03-30.xlsx
@@ -1757,16 +1757,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1775,14 +1775,14 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1972,14 +1972,14 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2151,32 +2151,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2386,58 +2386,58 @@
         <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>5.26</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
         <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
         <v>1.02</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AF10" t="n">
         <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
         <v>1.88</v>
@@ -2494,13 +2494,13 @@
         <v>1.27</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="BD10" t="n">
         <v>3.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="BF10" t="n">
         <v>1.12</v>
